--- a/lib/intake/__fixtures__/intake-sample-3.6.0.xlsx
+++ b/lib/intake/__fixtures__/intake-sample-3.6.0.xlsx
@@ -42509,7 +42509,7 @@
         <v/>
       </c>
       <c r="N160" s="863">
-        <f>IF(LEFT($B$155,8)="Existing","n/a — the existing service feeder is retained, so it is not sized or costed here",IF(LEFT($B$155,7)="Utility","n/a — the serving utility provides this run under its EV infrastructure rule, so it is not sized or costed here",IF(N($C160)=0,"no connected load on the equipment tab",IF($I160="","pick a conductor size",IF(N($K160)=0,"no ampacity on file for that size and material",IF(N($J160)=0,"enter the number of parallel sets",IF(N($L160)&lt;N($H160),"UNDERSIZED — "&amp;TEXT(N($L160),"#,##0")&amp;" A provided against a floor of "&amp;TEXT(N($H160),"#,##0")&amp;" A, set by "&amp;$B$154,IF(N($M160)&gt;$B$13,"ampacity OK, but voltage drop "&amp;TEXT(N($M160),"0.00%")&amp;" exceeds the allowance — ADVISORY","OK — "&amp;TEXT(N($L160),"#,##0")&amp;" A against a "&amp;TEXT(N($H160),"#,##0")&amp;" A floor; drop "&amp;TEXT(N($M160),"0.00%")&amp;" (ADVISORY). Priced as customer-side scope.")))))))</f>
+        <f>IF(LEFT($B$155,8)="Existing","n/a — the existing service feeder is retained, so it is not sized or costed here",IF(LEFT($B$155,7)="Utility","n/a — the serving utility provides this run under its EV infrastructure rule, so it is not sized or costed here",IF(N($C160)=0,"no connected load on the equipment tab",IF($I160="","pick a conductor size",IF(N($K160)=0,"no ampacity on file for that size and material",IF(N($J160)=0,"enter the number of parallel sets",IF(N($L160)&lt;N($H160),"UNDERSIZED — "&amp;TEXT(N($L160),"#,##0")&amp;" A provided against a floor of "&amp;TEXT(N($H160),"#,##0")&amp;" A, set by "&amp;$B$154,IF(N($M160)&gt;$B$13,"ampacity OK, but voltage drop "&amp;TEXT(N($M160),"0.00%")&amp;" exceeds the allowance — ADVISORY","OK — "&amp;TEXT(N($L160),"#,##0")&amp;" A against a "&amp;TEXT(N($H160),"#,##0")&amp;" A floor; drop "&amp;TEXT(N($M160),"0.00%")&amp;" (ADVISORY). Priced as customer-side scope."))))))))</f>
         <v/>
       </c>
       <c r="O160" s="804" t="n"/>
@@ -44032,11 +44032,11 @@
         </is>
       </c>
       <c r="B211" s="863">
-        <f>IF(Existing!$B$5="Greenfield — add load to existing service","n/a — no existing chargers",IF(Existing!$B$5="Greenfield — new service","n/a — greenfield",Existing!$B$16)</f>
+        <f>IF(Existing!$B$5="Greenfield — add load to existing service","n/a — no existing chargers",IF(Existing!$B$5="Greenfield — new service","n/a — greenfield",Existing!$B$16))</f>
         <v/>
       </c>
       <c r="C211" s="882">
-        <f>IF($B$211="n/a — no existing chargers","No existing chargers — this element is new and priced in full.",IF($B$211="n/a — greenfield","Greenfield — there is nothing to retain, so this line has no bearing on the take-off. The full electrical scope is priced.",IF($B$211="RETAIN","Zero the feeder conductor and equipment ground. The largest single saving on a replacement.",IF($B$211="NOT PRESENT","Not present on this site.","Price branch conductors at the placement distances entered above.")))</f>
+        <f>IF($B$211="n/a — no existing chargers","No existing chargers — this element is new and priced in full.",IF($B$211="n/a — greenfield","Greenfield — there is nothing to retain, so this line has no bearing on the take-off. The full electrical scope is priced.",IF($B$211="RETAIN","Zero the feeder conductor and equipment ground. The largest single saving on a replacement.",IF($B$211="NOT PRESENT","Not present on this site.","Price branch conductors at the placement distances entered above."))))</f>
         <v/>
       </c>
       <c r="I211" s="804" t="n"/>
@@ -44063,11 +44063,11 @@
         </is>
       </c>
       <c r="B212" s="863">
-        <f>IF(Existing!$B$5="Greenfield — add load to existing service","n/a — no existing chargers",IF(Existing!$B$5="Greenfield — new service","n/a — greenfield",Existing!$B$17)</f>
+        <f>IF(Existing!$B$5="Greenfield — add load to existing service","n/a — no existing chargers",IF(Existing!$B$5="Greenfield — new service","n/a — greenfield",Existing!$B$17))</f>
         <v/>
       </c>
       <c r="C212" s="882">
-        <f>IF($B$212="n/a — no existing chargers","No existing chargers — this element is new and priced in full.",IF($B$212="n/a — greenfield","Greenfield — there is nothing to retain, so this line has no bearing on the take-off. The full electrical scope is priced.",IF($B$212="RETAIN","Zero conduit, trenching, paving reinstatement and GPR. No ground is opened.",IF($B$212="NOT PRESENT","Not present on this site.","Price conduit and trenching in full.")))</f>
+        <f>IF($B$212="n/a — no existing chargers","No existing chargers — this element is new and priced in full.",IF($B$212="n/a — greenfield","Greenfield — there is nothing to retain, so this line has no bearing on the take-off. The full electrical scope is priced.",IF($B$212="RETAIN","Zero conduit, trenching, paving reinstatement and GPR. No ground is opened.",IF($B$212="NOT PRESENT","Not present on this site.","Price conduit and trenching in full."))))</f>
         <v/>
       </c>
       <c r="I212" s="804" t="n"/>
@@ -44094,11 +44094,11 @@
         </is>
       </c>
       <c r="B213" s="863">
-        <f>IF(Existing!$B$5="Greenfield — add load to existing service","n/a — no existing chargers",IF(Existing!$B$5="Greenfield — new service","n/a — greenfield",Existing!$B$18)</f>
+        <f>IF(Existing!$B$5="Greenfield — add load to existing service","n/a — no existing chargers",IF(Existing!$B$5="Greenfield — new service","n/a — greenfield",Existing!$B$18))</f>
         <v/>
       </c>
       <c r="C213" s="882">
-        <f>IF($B$213="n/a — no existing chargers","No existing chargers — this element is new and priced in full.",IF($B$213="n/a — greenfield","Greenfield — there is nothing to retain, so this line has no bearing on the take-off. The full electrical scope is priced.",IF($B$213="RETAIN","Rare. Breakers are normally replaced to match the new cabinet.",IF($B$213="NOT PRESENT","Not present on this site.","Price one breaker per new cabinet at the size on the Equipment tab.")))</f>
+        <f>IF($B$213="n/a — no existing chargers","No existing chargers — this element is new and priced in full.",IF($B$213="n/a — greenfield","Greenfield — there is nothing to retain, so this line has no bearing on the take-off. The full electrical scope is priced.",IF($B$213="RETAIN","Rare. Breakers are normally replaced to match the new cabinet.",IF($B$213="NOT PRESENT","Not present on this site.","Price one breaker per new cabinet at the size on the Equipment tab."))))</f>
         <v/>
       </c>
       <c r="I213" s="804" t="n"/>
@@ -44125,7 +44125,7 @@
         </is>
       </c>
       <c r="B214" s="810">
-        <f>IF(Existing!$B$5="Greenfield — add load to existing service","EXISTING SERVICE — no new service and no service feeder; price the distribution from the existing switchgear inward and the full charger scope",IF(Existing!$B$5="Greenfield — new service","GREENFIELD — price the full electrical scope",IF(AND(Existing!$B$13="RETAIN",Existing!$B$16="RETAIN",Existing!$B$17="RETAIN"),"CHARGER SWAP — electrical scope is breakers, terminations and commissioning only","PARTIAL REUSE — price only the elements marked REPLACE above"))</f>
+        <f>IF(Existing!$B$5="Greenfield — add load to existing service","EXISTING SERVICE — no new service and no service feeder; price the distribution from the existing switchgear inward and the full charger scope",IF(Existing!$B$5="Greenfield — new service","GREENFIELD — price the full electrical scope",IF(AND(Existing!$B$13="RETAIN",Existing!$B$16="RETAIN",Existing!$B$17="RETAIN"),"CHARGER SWAP — electrical scope is breakers, terminations and commissioning only","PARTIAL REUSE — price only the elements marked REPLACE above")))</f>
         <v/>
       </c>
       <c r="C214" s="814" t="inlineStr">
@@ -46491,7 +46491,7 @@
         </is>
       </c>
       <c r="B66" s="822">
-        <f>IF(Existing!$B$5="Greenfield — add load to existing service","GREENFIELD SITE WORKS ON AN EXISTING SERVICE — pads, trench and conduit from the existing switchgear; no service or transformer work",IF(Existing!$B$5="Greenfield — new service","GREENFIELD — full site works",IF(Existing!$B$17="RETAIN","PAD-AND-CHARGER SWAP — demolition, new pads, reinstatement and protection. No trenching, no paving beyond the pads.","PARTIAL — trenching required for the elements marked REPLACE"))</f>
+        <f>IF(Existing!$B$5="Greenfield — add load to existing service","GREENFIELD SITE WORKS ON AN EXISTING SERVICE — pads, trench and conduit from the existing switchgear; no service or transformer work",IF(Existing!$B$5="Greenfield — new service","GREENFIELD — full site works",IF(Existing!$B$17="RETAIN","PAD-AND-CHARGER SWAP — demolition, new pads, reinstatement and protection. No trenching, no paving beyond the pads.","PARTIAL — trenching required for the elements marked REPLACE")))</f>
         <v/>
       </c>
       <c r="C66" s="299" t="n"/>
